--- a/daily/2026-03-29.xlsx
+++ b/daily/2026-03-29.xlsx
@@ -32,7 +32,7 @@
       <color rgb="00E0E0E0"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +42,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E1E2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EF4444"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0022C55E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -65,6 +80,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -792,7 +810,6 @@
       <c r="V4" t="n">
         <v>14</v>
       </c>
-      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
         <v>2</v>
       </c>
@@ -870,7 +887,6 @@
       <c r="V5" t="n">
         <v>14</v>
       </c>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
         <v>48.6</v>
       </c>
@@ -1276,7 +1292,6 @@
       <c r="V10" t="n">
         <v>27</v>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="n">
         <v>-16.5</v>
       </c>
@@ -1354,7 +1369,6 @@
       <c r="V11" t="n">
         <v>27</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="n">
         <v>21.4</v>
       </c>
@@ -1514,7 +1528,6 @@
       <c r="V13" t="n">
         <v>27</v>
       </c>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="n">
         <v>38.6</v>
       </c>
@@ -1592,7 +1605,6 @@
       <c r="V14" t="n">
         <v>27</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="n">
         <v>26.1</v>
       </c>
@@ -1670,7 +1682,6 @@
       <c r="V15" t="n">
         <v>14</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="n">
         <v>11.8</v>
       </c>
@@ -2240,7 +2251,6 @@
       <c r="V22" t="n">
         <v>4</v>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="n">
         <v>-2.8</v>
       </c>
@@ -3384,7 +3394,6 @@
       <c r="V36" t="n">
         <v>23</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="n">
         <v>-3.6</v>
       </c>
@@ -3462,7 +3471,6 @@
       <c r="V37" t="n">
         <v>17</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="n">
         <v>7.1</v>
       </c>
@@ -3540,7 +3548,6 @@
       <c r="V38" t="n">
         <v>23</v>
       </c>
-      <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
         <v>0.4</v>
       </c>
@@ -3601,7 +3608,7 @@
         <v>53</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>-4.1</v>
@@ -3700,7 +3707,6 @@
       <c r="V40" t="n">
         <v>17</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="n">
         <v>-6.7</v>
       </c>
@@ -3860,7 +3866,6 @@
       <c r="V42" t="n">
         <v>30</v>
       </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="n">
         <v>26.6</v>
       </c>
@@ -3938,7 +3943,6 @@
       <c r="V43" t="n">
         <v>30</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="n">
         <v>17</v>
       </c>
@@ -4081,7 +4085,7 @@
         <v>47</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>-0.5</v>
@@ -4098,7 +4102,6 @@
       <c r="V45" t="n">
         <v>15</v>
       </c>
-      <c r="W45" t="inlineStr"/>
       <c r="X45" t="n">
         <v>20.1</v>
       </c>
@@ -4176,7 +4179,6 @@
       <c r="V46" t="n">
         <v>15</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
         <v>-11.1</v>
       </c>
@@ -4254,7 +4256,6 @@
       <c r="V47" t="n">
         <v>15</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="n">
         <v>15.9</v>
       </c>
@@ -4332,7 +4333,6 @@
       <c r="V48" t="n">
         <v>30</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="n">
         <v>4.6</v>
       </c>
@@ -4410,7 +4410,6 @@
       <c r="V49" t="n">
         <v>25</v>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="n">
         <v>-14.3</v>
       </c>
@@ -4734,7 +4733,6 @@
       <c r="V53" t="n">
         <v>25</v>
       </c>
-      <c r="W53" t="inlineStr"/>
       <c r="X53" t="n">
         <v>-9</v>
       </c>
@@ -5304,7 +5302,6 @@
       <c r="V60" t="n">
         <v>19</v>
       </c>
-      <c r="W60" t="inlineStr"/>
       <c r="X60" t="n">
         <v>21</v>
       </c>
@@ -5464,7 +5461,6 @@
       <c r="V62" t="n">
         <v>11</v>
       </c>
-      <c r="W62" t="inlineStr"/>
       <c r="X62" t="n">
         <v>6.1</v>
       </c>
@@ -5542,7 +5538,6 @@
       <c r="V63" t="n">
         <v>19</v>
       </c>
-      <c r="W63" t="inlineStr"/>
       <c r="X63" t="n">
         <v>-5</v>
       </c>
@@ -5620,7 +5615,6 @@
       <c r="V64" t="n">
         <v>11</v>
       </c>
-      <c r="W64" t="inlineStr"/>
       <c r="X64" t="n">
         <v>-4</v>
       </c>
@@ -5698,7 +5692,6 @@
       <c r="V65" t="n">
         <v>19</v>
       </c>
-      <c r="W65" t="inlineStr"/>
       <c r="X65" t="n">
         <v>45.8</v>
       </c>
@@ -5776,7 +5769,6 @@
       <c r="V66" t="n">
         <v>11</v>
       </c>
-      <c r="W66" t="inlineStr"/>
       <c r="X66" t="n">
         <v>0</v>
       </c>
@@ -5936,7 +5928,6 @@
       <c r="V68" t="n">
         <v>11</v>
       </c>
-      <c r="W68" t="inlineStr"/>
       <c r="X68" t="n">
         <v>-46.2</v>
       </c>
@@ -7162,7 +7153,6 @@
       <c r="V83" t="n">
         <v>26</v>
       </c>
-      <c r="W83" t="inlineStr"/>
       <c r="X83" t="n">
         <v>26.8</v>
       </c>
@@ -7404,7 +7394,6 @@
       <c r="V86" t="n">
         <v>26</v>
       </c>
-      <c r="W86" t="inlineStr"/>
       <c r="X86" t="n">
         <v>-1.2</v>
       </c>
@@ -7482,7 +7471,6 @@
       <c r="V87" t="n">
         <v>28</v>
       </c>
-      <c r="W87" t="inlineStr"/>
       <c r="X87" t="n">
         <v>0</v>
       </c>
@@ -7642,7 +7630,6 @@
       <c r="V89" t="n">
         <v>26</v>
       </c>
-      <c r="W89" t="inlineStr"/>
       <c r="X89" t="n">
         <v>-4.1</v>
       </c>
@@ -7966,7 +7953,6 @@
       <c r="V93" t="n">
         <v>26</v>
       </c>
-      <c r="W93" t="inlineStr"/>
       <c r="X93" t="n">
         <v>11.7</v>
       </c>
@@ -8536,7 +8522,6 @@
       <c r="V100" t="n">
         <v>3</v>
       </c>
-      <c r="W100" t="inlineStr"/>
       <c r="X100" t="n">
         <v>8.4</v>
       </c>
@@ -8696,7 +8681,6 @@
       <c r="V102" t="n">
         <v>3</v>
       </c>
-      <c r="W102" t="inlineStr"/>
       <c r="X102" t="n">
         <v>1.2</v>
       </c>
@@ -14475,2143 +14459,4841 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Darius Garland</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E2" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Garland scored 15 pts vs 19.5 line (-4.5), OVER missed by 4.5 pts. Minutes were as expected: 27 played vs L10 avg 29.2. Shooting was in line with averages: 55.6% FG (5/9, L10 avg 52.6%). Counter-signals that proved correct: H2H, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.2 pts — actual 15 was 5.2 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Kawhi Leonard</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="3" t="n">
         <v>26.5</v>
       </c>
+      <c r="E3" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Leonard scored 20 pts vs 26.5 line (-6.5), OVER missed by 6.5 pts. Leonard played 23 min (-8.3 vs L10 avg of 30.9) — 27% less than expected. Shooting was in line with averages: 50.0% FG (8/16, L10 avg 54.5%). Counter-signals that proved correct: Trend, H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 27.9 pts — actual 20 was 7.9 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Leonard for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>John Collins</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E4" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Collins scored 22 pts vs 12.5 line (+9.5), UNDER missed by 9.5 pts. Collins played 35 min (+11.0 vs L10 avg of 24.2) — 45% more than expected. Shooting efficiency was hot: 69.2% FG (+27.3% vs L10 avg of 41.9%). 9/13 from the field. Counter-signals that proved correct: Volume, HR L30, Context, Defense. Signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 7.9 pts — actual 22 was 14.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Brook Lopez</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E5" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Lopez scored 8 pts vs 10.5 line (-2.5), OVER missed by 2.5 pts. Minutes were as expected: 25 played vs L10 avg 27.6. Shooting efficiency was hot: 66.7% FG (+22.1% vs L10 avg of 44.6%). 2/3 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, Pace. Projection model targeted 14.8 pts — actual 8 was 6.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Derrick Jones Jr.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E6" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 13 pts vs 9.5 line (+3.5), UNDER missed by 3.5 pts. Jr. played 26 min (-3.9 vs L10 avg of 29.6) — 13% less than expected. Shooting efficiency was hot: 66.7% FG (+18.7% vs L10 avg of 48.0%). 6/9 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 6.3 pts — actual 13 was 6.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Bennedict Mathurin</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E7" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Mathurin scored 28 pts vs 17.5 line (+10.5), UNDER missed by 10.5 pts. Minutes were as expected: 27 played vs L10 avg 29.3. Shooting efficiency was hot: 70.0% FG (+25.1% vs L10 avg of 44.9%). 7/10 from the field. Counter-signals that proved correct: Volume, HR L10, Trend, Defense. Signals that were wrong: HR L30, Context, H2H. Projection model targeted 17.1 pts — actual 28 was 10.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Ousmane Dieng</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Dieng scored 7 pts vs 17.5 line (-10.5), UNDER hit by 10.5 pts. Dieng played 22 min (-7.3 vs L10 avg of 29.1) — 25% less than expected. Shooting was in line with averages: 37.5% FG (3/8, L10 avg 41.6%). Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (7/10 aligned). Counter-signals that were wrong: Trend, FG Trend, Min Trend. Projection model targeted 6.7 pts — actual 7 was 0.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Dieng in this role.</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Gary Trent Jr.</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E9" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 36 pts vs 17.5 line (+18.5), UNDER missed by 18.5 pts. Jr. played 37 min (+20.8 vs L10 avg of 16.5) — 126% more than expected. Shooting efficiency was hot: 57.1% FG (+28.9% vs L10 avg of 28.2%). 12/21 from the field. Counter-signals that proved correct: Trend, Defense, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 10.6 pts — actual 36 was 25.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Pete Nance</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Nance scored 5 pts vs 12.5 line (-7.5), UNDER hit by 7.5 pts. Nance played 38 min (+17.1 vs L10 avg of 21.4) — 80% more than expected. Shooting efficiency was cold: 22.2% FG (-18.0% vs L10 avg of 40.2%). 2/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: H2H, Min Trend. Projection model targeted 9.5 pts — actual 5 was 4.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>AJ Green</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E11" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Green scored 15 pts vs 11.5 line (+3.5), UNDER missed by 3.5 pts. Green played 28 min (+7.0 vs L10 avg of 21.1) — 33% more than expected. Shooting efficiency was hot: 50.0% FG (+7.6% vs L10 avg of 42.4%). 4/8 from the field. Counter-signals that proved correct: Defense, H2H, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 9.3 pts — actual 15 was 5.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Taurean Prince</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E12" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Prince scored 18 pts vs 10.5 line (+7.5), UNDER missed by 7.5 pts. Prince played 38 min (+17.8 vs L10 avg of 20.4) — 87% more than expected. Shooting efficiency was hot: 58.3% FG (+25.1% vs L10 avg of 33.2%). 7/12 from the field. Counter-signals that proved correct: Trend, H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.9 pts — actual 18 was 9.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Andre Jackson Jr.</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E13" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 13 pts vs 10.5 line (+2.5), UNDER missed by 2.5 pts. Jr. played 33 min (+24.4 vs L10 avg of 8.7) — 280% more than expected. Shooting efficiency was hot: 62.5% FG (+27.1% vs L10 avg of 35.4%). 5/8 from the field. Counter-signals that proved correct: Trend, Defense, H2H, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 4.0 pts — actual 13 was 9.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Jericho Sims</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sims scored 6 pts vs 8.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 23 played vs L10 avg 21.5. Shooting efficiency was cold: 60.0% FG (-27.1% vs L10 avg of 87.1%). 3/5 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (6/10 aligned). Counter-signals that were wrong: Trend, H2H, FG Trend. Projection model targeted 5.1 pts — actual 6 was 0.9 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Sims in this role.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Kris Dunn</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>LAC @ MIL</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E15" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Dunn scored 10 pts vs 5.5 line (+4.5), UNDER missed by 4.5 pts. Dunn played 32 min (+5.4 vs L10 avg of 26.2) — 21% more than expected. Shooting efficiency was hot: 80.0% FG (+42.1% vs L10 avg of 37.9%). 4/5 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, FG Trend, Min Trend. Projection model targeted 4.7 pts — actual 10 was 5.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Kel'el Ware</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Ware scored 5 pts vs 9.5 line (-4.5), UNDER hit by 4.5 pts. Ware played 15 min (-7.8 vs L10 avg of 22.9) — 34% less than expected. Shooting efficiency was cold: 40.0% FG (-7.5% vs L10 avg of 47.5%). 2/5 from the field. Signals that called it correctly: Trend, Context, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.5 pts — actual 5 was 3.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Ware's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Davion Mitchell</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E17" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Mitchell scored 12 pts vs 9.5 line (+2.5), UNDER missed by 2.5 pts. Mitchell played 36 min (+8.1 vs L10 avg of 27.4) — 30% more than expected. Shooting efficiency was hot: 71.4% FG (+21.3% vs L10 avg of 50.1%). 5/7 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 5.0 pts — actual 12 was 7.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Jarace Walker</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="5" t="n">
         <v>13.5</v>
       </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Pelle Larsson</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E19" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Larsson scored 15 pts vs 12.5 line (+2.5), UNDER missed by 2.5 pts. Larsson played 36 min (+5.3 vs L10 avg of 30.5) — 17% more than expected. Shooting efficiency was hot: 63.6% FG (+16.0% vs L10 avg of 47.6%). 7/11 from the field. Counter-signals that proved correct: Volume, HR L10, Defense, Pace. Signals that were wrong: HR L30, Trend, Context. Projection model targeted 10.7 pts — actual 15 was 4.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Andrew Wiggins</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E20" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Wiggins scored 15 pts vs 12.5 line (+2.5), OVER hit by 2.5 pts. Wiggins played 38 min (+11.0 vs L10 avg of 26.5) — 42% more than expected. Shooting efficiency was cold: 35.7% FG (-17.5% vs L10 avg of 53.2%). 5/14 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (7/10 aligned). Counter-signals that were wrong: HR L10, Trend, Min Trend. Projection model targeted 14.8 pts — actual 15 was 0.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Wiggins in this role.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Jaime Jaquez Jr.</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 17 pts vs 14.5 line (+2.5), UNDER missed by 2.5 pts. Minutes were as expected: 26 played vs L10 avg 26.3. Shooting efficiency was cold: 41.2% FG (-8.7% vs L10 avg of 49.9%). 7/17 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.7 pts — actual 17 was 5.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Jay Huff</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Huff scored 6 pts vs 9.5 line (-3.5), OVER missed by 3.5 pts. Huff played 16 min (-6.2 vs L10 avg of 22.3) — 28% less than expected. Shooting efficiency was hot: 60.0% FG (+13.1% vs L10 avg of 46.9%). 3/5 from the field. Counter-signals that proved correct: HR L10, Trend, Defense, H2H. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 10.8 pts — actual 6 was 4.8 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Huff for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Andrew Nembhard</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E23" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Nembhard scored 15 pts vs 15.5 line (-0.5), OVER missed by 0.5 pts. Nembhard played 36 min (+7.4 vs L10 avg of 29.0) — 26% more than expected. Shooting efficiency was hot: 50.0% FG (+5.3% vs L10 avg of 44.7%). 6/12 from the field. Counter-signals that proved correct: HR L10, Trend, H2H, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 17.6 pts — actual 15 was 2.6 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Bam Adebayo</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E24" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Adebayo scored 15 pts vs 22.5 line (-7.5), OVER missed by 7.5 pts. Adebayo played 33 min (-3.4 vs L10 avg of 36.4) — 9% less than expected. Shooting was in line with averages: 37.5% FG (6/16, L10 avg 38.3%). Counter-signals that proved correct: HR L30, HR L10, Trend, H2H. Signals that were wrong: Volume, Context, Defense. Projection model targeted 26.3 pts — actual 15 was 11.3 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Adebayo's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Tyler Herro</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="3" t="n">
         <v>22.5</v>
       </c>
+      <c r="E25" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Herro scored 31 pts vs 22.5 line (+8.5), UNDER missed by 8.5 pts. Herro played 36 min (+4.4 vs L10 avg of 32.0) — 14% more than expected. Shooting efficiency was hot: 54.5% FG (+8.2% vs L10 avg of 46.3%). 12/22 from the field. Counter-signals that proved correct: Defense, H2H, Pace, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 19.7 pts — actual 31 was 11.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>Pascal Siakam</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>MIA @ IND</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="E26" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Siakam scored 30 pts vs 22.5 line (+7.5), OVER hit by 7.5 pts. Minutes were as expected: 31 played vs L10 avg 30.6. Shooting was in line with averages: 45.8% FG (11/24, L10 avg 46.9%). Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 25.1 pts — actual 30 was 4.9 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Siakam's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>LaMelo Ball</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D27" s="3" t="n">
         <v>19.5</v>
       </c>
+      <c r="E27" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Ball scored 19 pts vs 19.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 26 played vs L10 avg 28.6. Shooting efficiency was cold: 36.8% FG (-8.1% vs L10 avg of 44.9%). 7/19 from the field. Counter-signals that proved correct: Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 26.4 pts — actual 19 was 7.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Payton Pritchard</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="D28" s="4" t="n">
         <v>18.5</v>
       </c>
+      <c r="E28" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Pritchard scored 28 pts vs 18.5 line (+9.5), OVER hit by 9.5 pts. Pritchard played 37 min (+4.0 vs L10 avg of 33.2) — 12% more than expected. Shooting efficiency was hot: 55.6% FG (+12.4% vs L10 avg of 43.2%). 10/18 from the field. Signals that called it correctly: Trend, FG Trend, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 19.3 pts — actual 28 was 8.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Pritchard's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>Coby White</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D29" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E29" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>WIN — White scored 11 pts vs 13.5 line (-2.5), UNDER hit by 2.5 pts. Minutes were as expected: 20 played vs L10 avg 20.5. Shooting efficiency was cold: 36.4% FG (-10.2% vs L10 avg of 46.6%). 4/11 from the field. Signals that called it correctly: Defense, Pace, Min Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.7 pts — actual 11 was 0.7 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for White in this role.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Baylor Scheierman</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="D30" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E30" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Scheierman scored 14 pts vs 6.5 line (+7.5), OVER hit by 7.5 pts. Minutes were as expected: 28 played vs L10 avg 27.1. Shooting efficiency was cold: 36.4% FG (-10.5% vs L10 avg of 46.9%). 4/11 from the field. Signals that called it correctly: Volume, Context, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 8.4 pts — actual 14 was 5.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Scheierman's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Miles Bridges</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="D31" s="4" t="n">
         <v>14.5</v>
       </c>
+      <c r="E31" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Bridges scored 14 pts vs 14.5 line (-0.5), UNDER hit by 0.5 pts. Minutes were as expected: 29 played vs L10 avg 29.4. Shooting efficiency was hot: 55.6% FG (+5.7% vs L10 avg of 49.9%). 5/9 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (8/10 aligned). Counter-signals that were wrong: FG Trend, Min Trend. Projection model targeted 5.2 pts — actual 14 was 8.8 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Neemias Queta</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="D32" s="3" t="n">
         <v>9.5</v>
       </c>
+      <c r="E32" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Queta scored 17 pts vs 9.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 29 played vs L10 avg 27.6. Shooting was in line with averages: 61.5% FG (8/13, L10 avg 59.0%). Counter-signals that proved correct: Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 6.3 pts — actual 17 was 10.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Derrick White</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D33" s="5" t="n">
         <v>17.5</v>
       </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Jayson Tatum</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D34" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E34" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Tatum scored 32 pts vs 24.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 31 played vs L10 avg 31.0. Shooting efficiency was hot: 52.2% FG (+14.0% vs L10 avg of 38.2%). 12/23 from the field. Counter-signals that proved correct: H2H. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 19.2 pts — actual 32 was 12.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Moussa Diabaté</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D35" t="n">
+      <c r="D35" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E35" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Diabaté scored 4 pts vs 7.5 line (-3.5), UNDER hit by 3.5 pts. Diabaté played 25 min (-3.2 vs L10 avg of 28.0) — 11% less than expected. Shooting efficiency was hot: 100.0% FG (+49.9% vs L10 avg of 50.1%). 2/2 from the field. Signals that called it correctly: HR L10, Context, Defense, H2H, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, Trend. Projection model targeted 6.1 pts — actual 4 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Diabaté's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>Brandon Miller</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D36" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E36" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Miller scored 13 pts vs 19.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 32 played vs L10 avg 31.3. Shooting efficiency was cold: 38.5% FG (-5.1% vs L10 avg of 43.6%). 5/13 from the field. Signals that called it correctly: Defense, Pace, FG Trend (3/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.3 pts — actual 13 was 3.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Miller's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>Luka Garza</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D37" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E37" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Garza scored 2 pts vs 7.5 line (-5.5), UNDER hit by 5.5 pts. Garza played 13 min (-3.8 vs L10 avg of 17.2) — 22% less than expected. Shooting efficiency was hot: 100.0% FG (+43.1% vs L10 avg of 56.9%). 1/1 from the field. Signals that called it correctly: HR L30, HR L10, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: Volume, Trend, H2H. Projection model targeted 7.4 pts — actual 2 was 5.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Garza's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Kon Knueppel</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="D38" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E38" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Knueppel scored 13 pts vs 17.5 line (-4.5), UNDER hit by 4.5 pts. Minutes were as expected: 32 played vs L10 avg 29.6. Shooting efficiency was cold: 38.5% FG (-5.7% vs L10 avg of 44.2%). 5/13 from the field. Signals that called it correctly: HR L10, Trend, Defense, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 17.4 pts — actual 13 was 4.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Knueppel's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>Sam Hauser</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="D39" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E39" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hauser scored 7 pts vs 9.5 line (-2.5), UNDER hit by 2.5 pts. Hauser played 34 min (+8.3 vs L10 avg of 25.3) — 33% more than expected. Shooting efficiency was hot: 50.0% FG (+16.2% vs L10 avg of 33.8%). 2/4 from the field. Signals that called it correctly: HR L10, Trend, Context, Defense, Pace (7/10 aligned). Counter-signals that were wrong: Volume, HR L30, H2H. Projection model targeted 9.1 pts — actual 7 was 2.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Hauser's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Jaylen Brown</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>BOS @ CHA</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D40" s="5" t="n">
         <v>22.5</v>
       </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Precious Achiuwa</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="D41" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E41" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Achiuwa scored 16 pts vs 13.5 line (+2.5), OVER hit by 2.5 pts. Achiuwa played 34 min (+3.8 vs L10 avg of 30.5) — 12% more than expected. Shooting efficiency was cold: 50.0% FG (-6.3% vs L10 avg of 56.3%). 7/14 from the field. Signals that called it correctly: HR L10, Trend, Defense, H2H, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 17.4 pts — actual 16 was 1.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Achiuwa in this role.</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Nique Clifford</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="3" t="n">
         <v>13.5</v>
       </c>
+      <c r="E42" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Clifford scored 17 pts vs 13.5 line (+3.5), UNDER missed by 3.5 pts. Clifford played 37 min (+5.2 vs L10 avg of 31.8) — 16% more than expected. Shooting efficiency was hot: 57.1% FG (+18.1% vs L10 avg of 39.0%). 8/14 from the field. Counter-signals that proved correct: Defense, H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.7 pts — actual 17 was 8.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Maxime Raynaud</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="D43" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E43" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Raynaud scored 13 pts vs 17.5 line (-4.5), OVER missed by 4.5 pts. Minutes were as expected: 32 played vs L10 avg 33.1. Shooting efficiency was cold: 40.0% FG (-17.2% vs L10 avg of 57.2%). 4/10 from the field. Counter-signals that proved correct: Volume, HR L30, Context, H2H. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 21.1 pts — actual 13 was 8.1 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Ziaire Williams</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D44" s="5" t="n">
         <v>12.5</v>
       </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n"/>
+      <c r="H44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Nolan Traore</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D45" t="n">
+      <c r="D45" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E45" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Traore scored 17 pts vs 10.5 line (+6.5), OVER hit by 6.5 pts. Traore played 30 min (+9.3 vs L10 avg of 20.6) — 45% more than expected. Shooting efficiency was hot: 46.2% FG (+19.2% vs L10 avg of 27.0%). 6/13 from the field. Signals that called it correctly: Context, Defense (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.0 pts — actual 17 was 1.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Traore in this role.</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Drake Powell</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D46" t="n">
+      <c r="D46" s="3" t="n">
         <v>8.5</v>
       </c>
+      <c r="E46" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Powell scored 16 pts vs 8.5 line (+7.5), UNDER missed by 7.5 pts. Powell played 28 min (+3.7 vs L10 avg of 24.6) — 15% more than expected. Shooting efficiency was hot: 75.0% FG (+36.0% vs L10 avg of 39.0%). 6/8 from the field. Counter-signals that proved correct: Defense, H2H, Pace, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 7.7 pts — actual 16 was 8.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Noah Clowney</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D47" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E47" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Clowney scored 15 pts vs 9.5 line (+5.5), OVER hit by 5.5 pts. Minutes were as expected: 20 played vs L10 avg 22.4. Shooting efficiency was hot: 45.5% FG (+9.3% vs L10 avg of 36.2%). 5/11 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense (4/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 10.4 pts — actual 15 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Clowney's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Devin Carter</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>SAC @ BKN</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D48" t="n">
+      <c r="D48" s="3" t="n">
         <v>15.5</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Carter scored 20 pts vs 15.5 line (+4.5), UNDER missed by 4.5 pts. Carter played 29 min (+9.6 vs L10 avg of 19.4) — 49% more than expected. Shooting efficiency was hot: 50.0% FG (+15.1% vs L10 avg of 34.9%). 6/12 from the field. Counter-signals that proved correct: Trend, Defense, H2H, FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.0 pts — actual 20 was 9.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Jamal Cain</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D49" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Cain scored 0 pts vs 8.5 line (-8.5), UNDER hit by 8.5 pts. Cain played 8 min (-8.8 vs L10 avg of 17.3) — 51% less than expected. Shooting efficiency was cold: 0.0% FG (-55.5% vs L10 avg of 55.5%). 0/3 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, H2H. Projection model targeted 2.7 pts — actual 0 was 2.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Cain's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Desmond Bane</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D50" t="n">
+      <c r="D50" s="3" t="n">
         <v>21.5</v>
       </c>
+      <c r="E50" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bane scored 17 pts vs 21.5 line (-4.5), OVER missed by 4.5 pts. Bane played 26 min (-8.2 vs L10 avg of 34.7) — 24% less than expected. Shooting was in line with averages: 50.0% FG (5/10, L10 avg 48.0%). Counter-signals that proved correct: HR L10, Trend, Defense, Pace. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 24.0 pts — actual 17 was 7.0 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Bane for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>Tristan da Silva</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D51" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E51" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Silva scored 12 pts vs 11.5 line (+0.5), OVER hit by 0.5 pts. Silva played 25 min (-6.5 vs L10 avg of 31.1) — 21% less than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 48.2%). Signals that called it correctly: HR L10, Trend, Context, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, Defense. Projection model targeted 13.0 pts — actual 12 was 1.0 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Silva in this role.</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Brandon Ingram</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D52" t="n">
+      <c r="D52" s="5" t="n">
         <v>22.5</v>
       </c>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n"/>
+      <c r="H52" s="5" t="inlineStr"/>
+      <c r="I52" s="5" t="n"/>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>Jalen Suggs</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D53" t="n">
+      <c r="D53" s="4" t="n">
         <v>13.5</v>
       </c>
+      <c r="E53" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Suggs scored 13 pts vs 13.5 line (-0.5), UNDER hit by 0.5 pts. Suggs played 26 min (-4.5 vs L10 avg of 30.4) — 15% less than expected. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 45.9%). Signals that called it correctly: Volume, Trend, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, H2H. Projection model targeted 7.4 pts — actual 13 was 5.6 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Suggs's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>RJ Barrett</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D54" t="n">
+      <c r="D54" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E54" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Barrett scored 24 pts vs 20.5 line (+3.5), UNDER missed by 3.5 pts. Barrett played 26 min (-4.1 vs L10 avg of 30.6) — 13% less than expected. Shooting was in line with averages: 57.1% FG (8/14, L10 avg 52.4%). Counter-signals that proved correct: HR L10, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, Trend. Projection model targeted 16.8 pts — actual 24 was 7.2 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Barrett for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Scottie Barnes</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D55" t="n">
+      <c r="D55" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E55" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Barnes scored 23 pts vs 18.5 line (+4.5), UNDER missed by 4.5 pts. Barnes played 28 min (-4.0 vs L10 avg of 32.4) — 12% less than expected. Shooting efficiency was hot: 64.3% FG (+9.3% vs L10 avg of 55.0%). 9/14 from the field. Counter-signals that proved correct: FG Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.6 pts — actual 23 was 9.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Ja'Kobe Walter</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D56" s="3" t="n">
         <v>10.5</v>
       </c>
+      <c r="E56" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Walter scored 11 pts vs 10.5 line (+0.5), UNDER missed by 0.5 pts. Walter played 28 min (+6.5 vs L10 avg of 21.6) — 30% more than expected. Shooting was in line with averages: 50.0% FG (4/8, L10 avg 52.4%). Counter-signals that proved correct: HR L10, Trend, Defense, FG Trend. Signals that were wrong: Volume, HR L30, Context. Projection model targeted 9.2 pts — actual 11 was 1.8 pts close (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Paolo Banchero</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D57" t="n">
+      <c r="D57" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>-15.5</v>
+      </c>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Banchero scored 9 pts vs 24.5 line (-15.5), OVER missed by 15.5 pts. Banchero played 30 min (-6.5 vs L10 avg of 36.4) — 18% less than expected. Shooting efficiency was cold: 21.4% FG (-21.5% vs L10 avg of 42.9%). 3/14 from the field. Counter-signals that proved correct: HR L30, Defense, Pace, FG Trend. Signals that were wrong: Volume, HR L10, Trend. Projection model targeted 24.5 pts — actual 9 was 15.5 pts off (wrong direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Banchero for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Jakob Poeltl</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D58" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E58" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Poeltl scored 11 pts vs 11.5 line (-0.5), OVER missed by 0.5 pts. Minutes were as expected: 25 played vs L10 avg 27.0. Shooting efficiency was hot: 71.4% FG (+7.4% vs L10 avg of 64.0%). 5/7 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Defense. Signals that were wrong: Trend, Context, H2H. Projection model targeted 12.5 pts — actual 11 was 1.5 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>Wendell Carter Jr.</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>ORL @ TOR</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D59" t="n">
+      <c r="D59" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E59" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 4 pts vs 11.5 line (-7.5), UNDER hit by 7.5 pts. Jr. played 26 min (-4.6 vs L10 avg of 30.4) — 15% less than expected. Shooting was in line with averages: 50.0% FG (1/2, L10 avg 54.5%). Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 10.4 pts — actual 4 was 6.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Jr.'s consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>Bilal Coulibaly</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D60" t="n">
+      <c r="D60" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E60" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Coulibaly scored 4 pts vs 12.5 line (-8.5), UNDER hit by 8.5 pts. Coulibaly played 24 min (-4.7 vs L10 avg of 28.8) — 16% less than expected. Shooting efficiency was cold: 14.3% FG (-30.6% vs L10 avg of 44.9%). 2/14 from the field. Signals that called it correctly: Volume, HR L30, Context, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 9.7 pts — actual 4 was 5.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Coulibaly's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>Donovan Clingan</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D61" t="n">
+      <c r="D61" s="4" t="n">
         <v>16.5</v>
       </c>
+      <c r="E61" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Clingan scored 6 pts vs 16.5 line (-10.5), UNDER hit by 10.5 pts. Clingan played 21 min (-6.9 vs L10 avg of 27.5) — 25% less than expected. Shooting was in line with averages: 50.0% FG (3/6, L10 avg 49.2%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 11.7 pts — actual 6 was 5.7 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Clingan's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Toumani Camara</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D62" t="n">
+      <c r="D62" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Camara scored 23 pts vs 14.5 line (+8.5), UNDER missed by 8.5 pts. Minutes were as expected: 28 played vs L10 avg 30.7. Shooting efficiency was hot: 57.1% FG (+9.3% vs L10 avg of 47.8%). 8/14 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 12.2 pts — actual 23 was 10.8 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Tristan Vukcevic</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D63" t="n">
+      <c r="D63" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E63" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Vukcevic scored 10 pts vs 11.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 16 played vs L10 avg 17.1. Shooting efficiency was cold: 40.0% FG (-9.7% vs L10 avg of 49.7%). 2/5 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, H2H. Signals that were wrong: Trend, Context, Defense. Projection model targeted 11.9 pts — actual 10 was 1.9 pts close (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Scoot Henderson</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D64" t="n">
+      <c r="D64" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E64" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Henderson scored 21 pts vs 16.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 25 played vs L10 avg 24.1. Shooting efficiency was hot: 54.5% FG (+10.6% vs L10 avg of 43.9%). 6/11 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 15.0 pts — actual 21 was 6.0 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>Will Riley</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D65" t="n">
+      <c r="D65" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E65" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Riley scored 14 pts vs 15.5 line (-1.5), UNDER hit by 1.5 pts. Riley played 26 min (-7.0 vs L10 avg of 32.6) — 21% less than expected. Shooting was in line with averages: 44.4% FG (4/9, L10 avg 43.9%). Signals that called it correctly: Volume, HR L30, Context, Pace, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 10.0 pts — actual 14 was 4.0 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Riley's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>Robert Williams III</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D66" t="n">
+      <c r="D66" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E66" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>WIN — III scored 4 pts vs 7.5 line (-3.5), UNDER hit by 3.5 pts. III played 15 min (-3.9 vs L10 avg of 18.8) — 21% less than expected. Shooting efficiency was hot: 66.7% FG (+6.2% vs L10 avg of 60.5%). 2/3 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted 6.4 pts — actual 4 was 2.4 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms III's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Jrue Holiday</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D67" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E67" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Holiday scored 11 pts vs 17.5 line (-6.5), UNDER hit by 6.5 pts. Holiday played 22 min (-7.8 vs L10 avg of 29.6) — 26% less than expected. Shooting efficiency was hot: 50.0% FG (+10.3% vs L10 avg of 39.7%). 3/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 10.9 pts — actual 11 was 0.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Holiday in this role.</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>Sidy Cissoko</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D68" t="n">
+      <c r="D68" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E68" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Cissoko scored 1 pts vs 7.5 line (-6.5), UNDER hit by 6.5 pts. Cissoko played 18 min (+4.3 vs L10 avg of 14.0) — 31% more than expected. Shooting efficiency was cold: 0.0% FG (-32.1% vs L10 avg of 32.1%). 0/1 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (7/10 aligned). Counter-signals that were wrong: Defense, H2H, Pace. Projection model targeted -0.1 pts — actual 1 was 1.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Cissoko in this role.</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>Deni Avdija</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>WAS @ POR</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D69" t="n">
+      <c r="D69" s="4" t="n">
         <v>26.5</v>
       </c>
+      <c r="E69" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Avdija scored 20 pts vs 26.5 line (-6.5), UNDER hit by 6.5 pts. Avdija played 28 min (-4.7 vs L10 avg of 32.3) — 15% less than expected. Shooting was in line with averages: 50.0% FG (8/16, L10 avg 45.6%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (6/10 aligned). Counter-signals that were wrong: Defense, Pace, FG Trend. Projection model targeted 13.2 pts — actual 20 was 6.8 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Avdija's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Alperen Sengun</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D70" t="n">
+      <c r="D70" s="3" t="n">
         <v>20.5</v>
       </c>
+      <c r="E70" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Sengun scored 36 pts vs 20.5 line (+15.5), UNDER missed by 15.5 pts. Minutes were as expected: 32 played vs L10 avg 32.2. Shooting efficiency was cold: 52.2% FG (-9.6% vs L10 avg of 61.8%). 12/23 from the field. Counter-signals that proved correct: Trend, Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 20.1 pts — actual 36 was 15.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>Reed Sheppard</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D71" t="n">
+      <c r="D71" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E71" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>-9.5</v>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Sheppard scored 6 pts vs 15.5 line (-9.5), UNDER hit by 9.5 pts. Sheppard played 21 min (-8.2 vs L10 avg of 29.5) — 28% less than expected. Shooting efficiency was cold: 33.3% FG (-5.1% vs L10 avg of 38.4%). 2/6 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (6/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 10.3 pts — actual 6 was 4.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Sheppard's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Kevin Durant</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D72" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E72" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Durant scored 20 pts vs 24.5 line (-4.5), OVER missed by 4.5 pts. Durant played 29 min (-7.1 vs L10 avg of 35.9) — 20% less than expected. Shooting efficiency was cold: 43.8% FG (-14.3% vs L10 avg of 58.1%). 7/16 from the field. Counter-signals that proved correct: Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 24.4 pts — actual 20 was 4.4 pts off (wrong direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Durant for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>Derik Queen</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D73" t="n">
+      <c r="D73" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E73" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Queen scored 13 pts vs 7.5 line (+5.5), OVER hit by 5.5 pts. Queen played 24 min (+5.7 vs L10 avg of 18.3) — 31% more than expected. Shooting was in line with averages: 41.7% FG (5/12, L10 avg 39.8%). Signals that called it correctly: Volume, HR L30, HR L10, Context, H2H (5/10 aligned). Counter-signals that were wrong: Trend, Defense, Pace. Projection model targeted 8.4 pts — actual 13 was 4.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Queen's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>Dejounte Murray</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D74" t="n">
+      <c r="D74" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E74" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Murray scored 19 pts vs 15.5 line (+3.5), OVER hit by 3.5 pts. Minutes were as expected: 28 played vs L10 avg 28.3. Shooting efficiency was hot: 57.1% FG (+9.0% vs L10 avg of 48.1%). 8/14 from the field. Signals that called it correctly: Volume, HR L30, Context, H2H, FG Trend (5/10 aligned). Counter-signals that were wrong: HR L10, Trend, Defense. Projection model targeted 20.1 pts — actual 19 was 1.1 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Murray in this role.</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>Herbert Jones</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D75" s="4" t="n">
         <v>9.5</v>
       </c>
+      <c r="E75" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jones scored 10 pts vs 9.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 30 played vs L10 avg 29.6. Shooting efficiency was cold: 30.0% FG (-10.8% vs L10 avg of 40.8%). 3/10 from the field. Signals that called it correctly: HR L10, Trend, H2H, FG Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 11.9 pts — actual 10 was 1.9 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Jones in this role.</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Amen Thompson</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D76" s="3" t="n">
         <v>18.5</v>
       </c>
+      <c r="E76" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Thompson scored 14 pts vs 18.5 line (-4.5), OVER missed by 4.5 pts. Thompson played 35 min (-3.9 vs L10 avg of 38.8) — 10% less than expected. Shooting efficiency was cold: 50.0% FG (-5.5% vs L10 avg of 55.5%). 5/10 from the field. Counter-signals that proved correct: Volume, HR L30, Context, H2H. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 18.9 pts — actual 14 was 4.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>Tari Eason</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D77" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E77" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Eason scored 15 pts vs 8.5 line (+6.5), OVER hit by 6.5 pts. Minutes were as expected: 22 played vs L10 avg 24.6. Shooting efficiency was hot: 50.0% FG (+19.9% vs L10 avg of 30.1%). 6/12 from the field. Signals that called it correctly: Volume, HR L30, Context, Defense, H2H (6/10 aligned). Counter-signals that were wrong: HR L10, Trend, FG Trend. Projection model targeted 8.4 pts — actual 15 was 6.6 pts off (wrong direction). Result classification: MODEL_CORRECT. Note: Result confirms Eason's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>Zion Williamson</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D78" t="n">
+      <c r="D78" s="4" t="n">
         <v>20.5</v>
       </c>
+      <c r="E78" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Williamson scored 18 pts vs 20.5 line (-2.5), UNDER hit by 2.5 pts. Williamson played 25 min (-5.3 vs L10 avg of 30.6) — 17% less than expected. Shooting was in line with averages: 75.0% FG (6/8, L10 avg 71.6%). Signals that called it correctly: Volume, Context, Defense, H2H, Pace (5/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 16.0 pts — actual 18 was 2.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Williamson in this role.</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Jabari Smith Jr.</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D79" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E79" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Jr. scored 20 pts vs 15.5 line (+4.5), OVER hit by 4.5 pts. Jr. played 33 min (-4.0 vs L10 avg of 37.3) — 11% less than expected. Shooting was in line with averages: 46.7% FG (7/15, L10 avg 43.5%). Signals that called it correctly: Volume, HR L30, HR L10, Trend, Context (9/10 aligned). Counter-signals that were wrong: FG Trend. Projection model targeted 17.4 pts — actual 20 was 2.6 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Strong signal alignment (9/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>Trey Murphy III</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="5" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D80" s="5" t="n">
         <v>20.5</v>
       </c>
+      <c r="E80" s="5" t="n"/>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="n"/>
+      <c r="H80" s="5" t="inlineStr"/>
+      <c r="I80" s="5" t="n"/>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>Saddiq Bey</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>HOU @ NOP</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D81" t="n">
+      <c r="D81" s="4" t="n">
         <v>17.5</v>
       </c>
+      <c r="E81" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Bey scored 18 pts vs 17.5 line (+0.5), OVER hit by 0.5 pts. Minutes were as expected: 31 played vs L10 avg 31.8. Shooting efficiency was hot: 53.8% FG (+10.8% vs L10 avg of 43.0%). 7/13 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context (4/10 aligned). Counter-signals that were wrong: Trend, Defense, H2H. Projection model targeted 17.6 pts — actual 18 was 0.4 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Bey in this role.</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Jalen Brunson</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D82" t="n">
+      <c r="D82" s="3" t="n">
         <v>24.5</v>
       </c>
+      <c r="E82" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H82" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Brunson scored 32 pts vs 24.5 line (+7.5), UNDER missed by 7.5 pts. Minutes were as expected: 37 played vs L10 avg 36.8. Shooting efficiency was hot: 59.1% FG (+15.5% vs L10 avg of 43.6%). 13/22 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Min Trend. Signals that were wrong: Volume, Context, Defense. Projection model targeted 18.1 pts — actual 32 was 13.9 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I82" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Alex Caruso</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D83" t="n">
+      <c r="D83" s="3" t="n">
         <v>5.5</v>
       </c>
+      <c r="E83" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Caruso scored 6 pts vs 5.5 line (+0.5), UNDER missed by 0.5 pts. Minutes were as expected: 18 played vs L10 avg 17.7. Shooting was in line with averages: 40.0% FG (2/5, L10 avg 43.7%). Counter-signals that proved correct: Volume, HR L30, HR L10, Context. Signals that were wrong: Trend, Defense, Pace. Projection model targeted 3.4 pts — actual 6 was 2.6 pts off (correct direction). Loss classification: CLOSE_CALL. Note: Within 2 pts — direction was sound. Small execution variance, no model adjustment needed.</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Mikal Bridges</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D84" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E84" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Bridges scored 15 pts vs 12.5 line (+2.5), UNDER missed by 2.5 pts. Bridges played 34 min (+4.3 vs L10 avg of 29.9) — 14% more than expected. Shooting efficiency was hot: 54.5% FG (+18.9% vs L10 avg of 35.6%). 6/11 from the field. Counter-signals that proved correct: Volume, H2H. Signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 9.5 pts — actual 15 was 5.5 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Luguentz Dort</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>LEAN UNDER</t>
         </is>
       </c>
-      <c r="D85" t="n">
+      <c r="D85" s="3" t="n">
         <v>6.5</v>
       </c>
+      <c r="E85" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Dort scored 12 pts vs 6.5 line (+5.5), UNDER missed by 5.5 pts. Minutes were as expected: 27 played vs L10 avg 25.2. Shooting efficiency was hot: 57.1% FG (+30.0% vs L10 avg of 27.1%). 4/7 from the field. Counter-signals that proved correct: Volume, HR L30, Context, H2H. Signals that were wrong: HR L10, Trend, Defense. Projection model targeted 6.8 pts — actual 12 was 5.2 pts off (wrong direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>Ajay Mitchell</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D86" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E86" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Mitchell scored 8 pts vs 11.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 24 played vs L10 avg 25.3. Shooting was in line with averages: 50.0% FG (2/4, L10 avg 51.6%). Signals that called it correctly: Trend, Defense, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 8.4 pts — actual 8 was 0.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Mitchell in this role.</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Mitchell Robinson</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D87" t="n">
+      <c r="D87" s="3" t="n">
         <v>4.5</v>
       </c>
+      <c r="E87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H87" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Robinson scored 3 pts vs 4.5 line (-1.5), OVER missed by 1.5 pts. Robinson played 18 min (-3.3 vs L10 avg of 20.8) — 16% less than expected. Shooting efficiency was cold: 33.3% FG (-48.4% vs L10 avg of 81.7%). 1/3 from the field. Counter-signals that proved correct: Defense, H2H, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.7 pts — actual 3 was 2.7 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>Isaiah Hartenstein</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D88" t="n">
+      <c r="D88" s="4" t="n">
         <v>7.5</v>
       </c>
+      <c r="E88" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hartenstein scored 6 pts vs 7.5 line (-1.5), UNDER hit by 1.5 pts. Minutes were as expected: 24 played vs L10 avg 22.4. Shooting efficiency was hot: 50.0% FG (+11.5% vs L10 avg of 38.5%). 3/6 from the field. Signals that called it correctly: HR L10, Trend, Context, Defense, H2H (8/10 aligned). Counter-signals that were wrong: Volume, HR L30. Projection model targeted 1.2 pts — actual 6 was 4.8 pts off (correct direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Jalen Williams</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D89" s="3" t="n">
         <v>16.5</v>
       </c>
+      <c r="E89" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="F89" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H89" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Williams scored 22 pts vs 16.5 line (+5.5), UNDER missed by 5.5 pts. Williams played 29 min (+3.2 vs L10 avg of 25.4) — 13% more than expected. Shooting efficiency was hot: 63.6% FG (+12.2% vs L10 avg of 51.4%). 7/11 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: Defense, Pace, Min Trend. Projection model targeted 14.7 pts — actual 22 was 7.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Karl-Anthony Towns</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D90" t="n">
+      <c r="D90" s="3" t="n">
         <v>17.5</v>
       </c>
+      <c r="E90" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Towns scored 15 pts vs 17.5 line (-2.5), OVER missed by 2.5 pts. Towns played 34 min (+5.0 vs L10 avg of 29.1) — 17% more than expected. Shooting was in line with averages: 55.6% FG (5/9, L10 avg 56.7%). Counter-signals that proved correct: Defense, Pace. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 18.0 pts — actual 15 was 3.0 pts off (correct direction). Loss classification: MODEL_FAILURE. Note: Model signals were misleading for this matchup — review Towns's recent role and usage for pattern shifts.</t>
+        </is>
+      </c>
+      <c r="I90" s="3" t="inlineStr">
+        <is>
+          <t>MODEL_FAILURE</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>Cason Wallace</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D91" s="4" t="n">
         <v>6.5</v>
       </c>
+      <c r="E91" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Wallace scored 5 pts vs 6.5 line (-1.5), UNDER hit by 1.5 pts. Wallace played 15 min (-9.6 vs L10 avg of 24.7) — 39% less than expected. Shooting efficiency was hot: 50.0% FG (+6.4% vs L10 avg of 43.6%). 2/4 from the field. Signals that called it correctly: HR L10, Trend, Defense, H2H, Pace (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 4.7 pts — actual 5 was 0.3 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Wallace in this role.</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>Josh Hart</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D92" t="n">
+      <c r="D92" s="4" t="n">
         <v>12.5</v>
       </c>
+      <c r="E92" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Hart scored 15 pts vs 12.5 line (+2.5), OVER hit by 2.5 pts. Hart played 34 min (+3.6 vs L10 avg of 30.2) — 12% more than expected. Shooting efficiency was cold: 55.6% FG (-5.3% vs L10 avg of 60.9%). 5/9 from the field. Signals that called it correctly: Trend, Context, H2H, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.0 pts — actual 15 was 2.0 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Hart in this role.</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>Chet Holmgren</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D93" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E93" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Holmgren scored 16 pts vs 15.5 line (+0.5), OVER hit by 0.5 pts. Holmgren played 33 min (+4.3 vs L10 avg of 28.4) — 15% more than expected. Shooting was in line with averages: 50.0% FG (5/10, L10 avg 52.9%). Signals that called it correctly: Volume, HR L10, Context, FG Trend (4/10 aligned). Counter-signals that were wrong: HR L30, Trend, Defense. Projection model targeted 26.1 pts — actual 16 was 10.1 pts off (correct direction). Result classification: CLOSE_CALL. Note: Result confirms Holmgren's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>Shai Gilgeous-Alexander</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D94" s="4" t="n">
         <v>30.5</v>
       </c>
+      <c r="E94" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Gilgeous-Alexander scored 30 pts vs 30.5 line (-0.5), UNDER hit by 0.5 pts. Gilgeous-Alexander played 37 min (+3.3 vs L10 avg of 33.5) — 10% more than expected. Shooting efficiency was cold: 44.4% FG (-15.6% vs L10 avg of 60.0%). 8/18 from the field. Signals that called it correctly: HR L30, Trend, Context, Defense, Pace (5/10 aligned). Counter-signals that were wrong: Volume, HR L10, H2H. Projection model targeted 29.4 pts — actual 30 was 0.6 pts close (correct direction). Result classification: CLOSE_CALL. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Gilgeous-Alexander in this role.</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>OG Anunoby</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>NYK @ OKC</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D95" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E95" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Anunoby scored 10 pts vs 15.5 line (-5.5), UNDER hit by 5.5 pts. Minutes were as expected: 33 played vs L10 avg 34.1. Shooting efficiency was cold: 22.2% FG (-32.4% vs L10 avg of 54.6%). 2/9 from the field. Signals that called it correctly: Trend, Defense, H2H, Pace (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.5 pts — actual 10 was 3.5 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Anunoby's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>Cameron Johnson</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B96" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="4" t="n">
         <v>11.5</v>
       </c>
+      <c r="E96" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Johnson scored 6 pts vs 11.5 line (-5.5), UNDER hit by 5.5 pts. Johnson played 19 min (-11.2 vs L10 avg of 30.3) — 37% less than expected. Shooting efficiency was cold: 40.0% FG (-15.9% vs L10 avg of 55.9%). 2/5 from the field. Signals that called it correctly: Context, Defense, H2H, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 5.6 pts — actual 6 was 0.4 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Johnson in this role.</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>Brandin Podziemski</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D97" t="n">
+      <c r="D97" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E97" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Podziemski scored 23 pts vs 15.5 line (+7.5), OVER hit by 7.5 pts. Minutes were as expected: 32 played vs L10 avg 31.8. Shooting efficiency was hot: 57.1% FG (+16.6% vs L10 avg of 40.5%). 8/14 from the field. Signals that called it correctly: Trend, Pace, FG Trend, Min Trend (4/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 16.9 pts — actual 23 was 6.1 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Podziemski's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Tim Hardaway Jr.</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D98" t="n">
+      <c r="D98" s="3" t="n">
         <v>11.5</v>
       </c>
+      <c r="E98" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jr. scored 16 pts vs 11.5 line (+4.5), UNDER missed by 4.5 pts. Minutes were as expected: 26 played vs L10 avg 24.3. Shooting efficiency was hot: 50.0% FG (+15.1% vs L10 avg of 34.9%). 5/10 from the field. Counter-signals that proved correct: Volume, HR L30, HR L10, Trend. Signals that were wrong: H2H, FG Trend, Min Trend. Projection model targeted 7.7 pts — actual 16 was 8.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I98" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Peyton Watson</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D99" t="n">
+      <c r="D99" s="3" t="n">
         <v>12.5</v>
       </c>
+      <c r="E99" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Watson scored 10 pts vs 12.5 line (-2.5), OVER missed by 2.5 pts. Watson played 22 min (-9.5 vs L10 avg of 31.8) — 30% less than expected. Shooting efficiency was cold: 27.3% FG (-18.7% vs L10 avg of 46.0%). 3/11 from the field. Counter-signals that proved correct: Trend, H2H, FG Trend, Min Trend. Signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 13.6 pts — actual 10 was 3.6 pts off (correct direction). Loss classification: MINUTES_SHORTFALL. Note: Minutes were the deciding factor, not scoring rate. Flag Watson for minutes risk in future props if role uncertainty exists.</t>
+        </is>
+      </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>MINUTES_SHORTFALL</t>
+        </is>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>Kristaps Porziņģis</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D100" t="n">
+      <c r="D100" s="4" t="n">
         <v>19.5</v>
       </c>
+      <c r="E100" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Porziņģis scored 23 pts vs 19.5 line (+3.5), OVER hit by 3.5 pts. Porziņģis played 29 min (+5.9 vs L10 avg of 22.7) — 26% more than expected. Shooting efficiency was hot: 57.1% FG (+15.2% vs L10 avg of 41.9%). 8/14 from the field. Signals that called it correctly: Defense, Pace (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 21.8 pts — actual 23 was 1.2 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Porziņģis in this role.</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>Gui Santos</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D101" t="n">
+      <c r="D101" s="4" t="n">
         <v>15.5</v>
       </c>
+      <c r="E101" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Santos scored 9 pts vs 15.5 line (-6.5), UNDER hit by 6.5 pts. Minutes were as expected: 32 played vs L10 avg 31.7. Shooting efficiency was cold: 33.3% FG (-13.9% vs L10 avg of 47.2%). 3/9 from the field. Signals that called it correctly: Volume, Context, H2H, FG Trend (4/10 aligned). Counter-signals that were wrong: HR L30, HR L10, Trend. Projection model targeted 14.0 pts — actual 9 was 5.0 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Santos's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>De'Anthony Melton</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D102" t="n">
+      <c r="D102" s="3" t="n">
         <v>14.5</v>
       </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G102" s="3" t="n">
+        <v>-14.5</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Melton scored 0 pts vs 14.5 line (-14.5), OVER missed by 14.5 pts. Minutes were as expected: 25 played vs L10 avg 24.9. Shooting efficiency was cold: 0.0% FG (-36.4% vs L10 avg of 36.4%). 0/5 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend, Defense. Signals that were wrong: Volume, Context, Pace. Projection model targeted 21.3 pts — actual 0 was 21.3 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>Christian Braun</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>LEAN OVER</t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D103" s="4" t="n">
         <v>10.5</v>
       </c>
+      <c r="E103" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Braun scored 12 pts vs 10.5 line (+1.5), OVER hit by 1.5 pts. Minutes were as expected: 33 played vs L10 avg 30.6. Shooting efficiency was hot: 62.5% FG (+5.2% vs L10 avg of 57.3%). 5/8 from the field. Signals that called it correctly: Volume, HR L30, HR L10, Context, Defense (8/10 aligned). Counter-signals that were wrong: Trend, Min Trend. Projection model targeted 10.4 pts — actual 12 was 1.6 pts close (wrong direction). Result classification: CLOSE_CALL. Note: Strong signal alignment (8/10) with confirmed result — this player/matchup pattern is reliable for future predictions.</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>CLOSE_CALL</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>Draymond Green</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D104" t="n">
+      <c r="D104" s="4" t="n">
         <v>8.5</v>
       </c>
+      <c r="E104" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Green scored 13 pts vs 8.5 line (+4.5), OVER hit by 4.5 pts. Minutes were as expected: 30 played vs L10 avg 30.7. Shooting was in line with averages: 45.5% FG (5/11, L10 avg 43.1%). Signals that called it correctly: Context, Defense, H2H, Pace, FG Trend (6/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 11.7 pts — actual 13 was 1.3 pts close (correct direction). Result classification: MODEL_CORRECT. Note: Projection model accuracy within 2 pts — GBR features are well-calibrated for Green in this role.</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
+      <c r="A105" s="5" t="inlineStr">
         <is>
           <t>Aaron Gordon</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B105" s="5" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="5" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D105" t="n">
+      <c r="D105" s="5" t="n">
         <v>15.5</v>
       </c>
+      <c r="E105" s="5" t="n"/>
+      <c r="F105" s="5" t="inlineStr">
+        <is>
+          <t>DNP</t>
+        </is>
+      </c>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="inlineStr"/>
+      <c r="I105" s="5" t="n"/>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>Jamal Murray</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B106" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="4" t="inlineStr">
         <is>
           <t>UNDER</t>
         </is>
       </c>
-      <c r="D106" t="n">
+      <c r="D106" s="4" t="n">
         <v>23.5</v>
       </c>
+      <c r="E106" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>WIN — Murray scored 20 pts vs 23.5 line (-3.5), UNDER hit by 3.5 pts. Minutes were as expected: 34 played vs L10 avg 36.4. Shooting efficiency was hot: 58.3% FG (+12.0% vs L10 avg of 46.3%). 7/12 from the field. Signals that called it correctly: H2H, FG Trend (2/10 aligned). Counter-signals that were wrong: Volume, HR L30, HR L10. Projection model targeted 22.2 pts — actual 20 was 2.2 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms Murray's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Nikola Jokić</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D107" s="3" t="n">
         <v>26.5</v>
       </c>
+      <c r="E107" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>LOSS — Jokić scored 25 pts vs 26.5 line (-1.5), OVER missed by 1.5 pts. Minutes were as expected: 36 played vs L10 avg 35.9. Shooting efficiency was cold: 50.0% FG (-7.0% vs L10 avg of 57.0%). 10/20 from the field. Counter-signals that proved correct: HR L30, HR L10, Trend. Signals that were wrong: Volume, Context, Defense. Projection model targeted 28.4 pts — actual 25 was 3.4 pts off (correct direction). Loss classification: SHOOTING_VARIANCE. Note: Volume and opportunity signals were correct but shooting efficiency diverged. Normal variance — per-minute output was on track.</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>SHOOTING_VARIANCE</t>
+        </is>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>Gary Payton II</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B108" s="4" t="inlineStr">
         <is>
           <t>GSW @ DEN</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="4" t="inlineStr">
         <is>
           <t>OVER</t>
         </is>
       </c>
-      <c r="D108" t="n">
+      <c r="D108" s="4" t="n">
         <v>11.5</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>WIN — II scored 16 pts vs 11.5 line (+4.5), OVER hit by 4.5 pts. Minutes were as expected: 21 played vs L10 avg 23.4. Shooting efficiency was hot: 87.5% FG (+17.4% vs L10 avg of 70.1%). 7/8 from the field. Signals that called it correctly: HR L10, Trend, Pace, FG Trend, Min Trend (5/10 aligned). Counter-signals that were wrong: Volume, HR L30, Context. Projection model targeted 13.7 pts — actual 16 was 2.3 pts off (correct direction). Result classification: MODEL_CORRECT. Note: Result confirms II's consistency near this line level.</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>MODEL_CORRECT</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-30 06:00</t>
+        </is>
       </c>
     </row>
   </sheetData>
